--- a/app_scm_data.xlsx
+++ b/app_scm_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4E8A11-8BBD-42F3-8E14-8ABB89264CF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2D35C6-185B-42AE-89DB-9B29FDEE77DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
@@ -184,12 +184,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -211,7 +217,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -232,6 +238,9 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3428,7 +3437,7 @@
       <c r="N43" s="1">
         <v>4080</v>
       </c>
-      <c r="O43">
+      <c r="O43" s="1">
         <f>O42*(1-0.0106)</f>
         <v>4.9964699999999995</v>
       </c>
@@ -3440,6 +3449,21 @@
       </c>
       <c r="R43" s="3">
         <v>0.73</v>
+      </c>
+      <c r="S43" s="12">
+        <v>563.75</v>
+      </c>
+      <c r="T43" s="12">
+        <v>2460.67</v>
+      </c>
+      <c r="U43" s="12">
+        <v>2674.5</v>
+      </c>
+      <c r="V43" s="12">
+        <v>1798.5</v>
+      </c>
+      <c r="W43" s="12">
+        <v>1798.5</v>
       </c>
     </row>
   </sheetData>

--- a/app_scm_data.xlsx
+++ b/app_scm_data.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\Supply Chain\Gestão\Reportes\Relatório Mensal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2D35C6-185B-42AE-89DB-9B29FDEE77DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D7FBAC-EC48-4AA1-A4E2-DB52B809D3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{19CE77E3-4AC1-43FA-889F-0CF0F915B873}"/>
   </bookViews>
   <sheets>
     <sheet name="Final" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -184,18 +184,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -217,7 +211,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -238,9 +232,6 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3450,20 +3441,20 @@
       <c r="R43" s="3">
         <v>0.73</v>
       </c>
-      <c r="S43" s="12">
+      <c r="S43" s="4">
         <v>563.75</v>
       </c>
-      <c r="T43" s="12">
-        <v>2460.67</v>
-      </c>
-      <c r="U43" s="12">
+      <c r="T43" s="4">
+        <v>6770</v>
+      </c>
+      <c r="U43" s="4">
         <v>2674.5</v>
       </c>
-      <c r="V43" s="12">
-        <v>1798.5</v>
-      </c>
-      <c r="W43" s="12">
-        <v>1798.5</v>
+      <c r="V43" s="4">
+        <v>2199.5</v>
+      </c>
+      <c r="W43" s="4">
+        <v>2212</v>
       </c>
     </row>
   </sheetData>
